--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484266_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484266_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1702</v>
+        <v>4.6231</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9051</v>
+        <v>4.8957</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2651</v>
+        <v>-0.2726</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.8312</v>
+        <v>2.8819</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.4111</v>
+        <v>0.0215</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5799</v>
+        <v>2.8604</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5244</v>
+        <v>5.5674</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2135</v>
+        <v>2.4367</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3109</v>
+        <v>3.1307</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3556</v>
+        <v>-2.6854</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.6247</v>
+        <v>-2.4152</v>
       </c>
       <c r="O2" t="n">
-        <v>0.269</v>
+        <v>-0.2702</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R2" t="n">
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4088</v>
+        <v>0.2332</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5963</v>
+        <v>0.3599</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8125</v>
+        <v>-0.1267</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9833</v>
+        <v>-0.0549</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7145</v>
+        <v>-0.0549</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.842</v>
+        <v>4.2192</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4017</v>
+        <v>4.8062</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5597</v>
+        <v>-0.5869</v>
       </c>
       <c r="G3" t="n">
         <v>2.4569</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5712</v>
+        <v>-0.194</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3494</v>
+        <v>0.0551</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2218</v>
+        <v>-0.2491</v>
       </c>
       <c r="V3" t="n">
         <v>1.7609</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7846</v>
+        <v>2.0808</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3296</v>
+        <v>3.0599</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.545</v>
+        <v>-0.9791</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8819</v>
+        <v>3.2519</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0215</v>
+        <v>0.6621</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8604</v>
+        <v>2.5898</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5674</v>
+        <v>3.2063</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4367</v>
+        <v>1.2906</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1307</v>
+        <v>1.9157</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6854</v>
+        <v>0.0456</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4152</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2702</v>
+        <v>0.6741</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6052</v>
+        <v>-0.1245</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2062</v>
+        <v>-0.1464</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.399</v>
+        <v>0.0219</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0549</v>
+        <v>-1.8279</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6781</v>
+        <v>1.4208</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4938</v>
+        <v>1.3506</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8157</v>
+        <v>0.0701</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2519</v>
+        <v>0.4848</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6621</v>
+        <v>-1.4303</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5898</v>
+        <v>1.9151</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2063</v>
+        <v>1.268</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2906</v>
+        <v>-0.243</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9157</v>
+        <v>1.511</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0456</v>
+        <v>-0.7832</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.1872</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6741</v>
+        <v>0.4041</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5272</v>
+        <v>-0.3728</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7125</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1853</v>
+        <v>-0.4555</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8279</v>
+        <v>0.3321</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8279</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2846</v>
+        <v>1.3837</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3506</v>
+        <v>2.8331</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.066</v>
+        <v>-1.4494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4848</v>
+        <v>0.979</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4303</v>
+        <v>0.8174</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9151</v>
+        <v>0.1617</v>
       </c>
       <c r="J6" t="n">
-        <v>1.268</v>
+        <v>1.4729</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.243</v>
+        <v>1.3111</v>
       </c>
       <c r="L6" t="n">
-        <v>1.511</v>
+        <v>0.1619</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7832</v>
+        <v>-0.4939</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1872</v>
+        <v>-0.4937</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4041</v>
+        <v>-0.0002</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.509</v>
+        <v>-0.3962</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.1004</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5917</v>
+        <v>-0.2958</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3321</v>
+        <v>0.9962</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3321</v>
+        <v>-1.441</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9908</v>
+        <v>1.3331</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6309</v>
+        <v>1.64</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.64</v>
+        <v>-0.3068</v>
       </c>
       <c r="G7" t="n">
-        <v>0.979</v>
+        <v>-1.8312</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8174</v>
+        <v>-2.4111</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1617</v>
+        <v>0.5799</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4729</v>
+        <v>0.5244</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3111</v>
+        <v>0.2135</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>0.3109</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4939</v>
+        <v>-2.3556</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4937</v>
+        <v>-2.6247</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002</v>
+        <v>0.269</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7891</v>
+        <v>1.5717</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3026</v>
+        <v>1.3312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4865</v>
+        <v>0.2405</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9962</v>
+        <v>1.9833</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4373</v>
+        <v>2.7145</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.441</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2205</v>
+        <v>0.0828</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6679</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>-0.8885</v>
@@ -1078,10 +1078,10 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.3033</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3033</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3531</v>
+        <v>-0.9464</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1708</v>
+        <v>-0.0092</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1824</v>
+        <v>-0.9372</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8032</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6234</v>
+        <v>-0.2166</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1127</v>
+        <v>0.0489</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5107</v>
+        <v>-0.2656</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1219</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0975</v>
+        <v>-2.4009</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2981</v>
+        <v>-2.6015</v>
       </c>
       <c r="F10" t="n">
         <v>0.2006</v>
@@ -1234,10 +1234,10 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5723</v>
+        <v>0.2689</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7567</v>
+        <v>0.4534</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1845</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.063</v>
+        <v>-2.4775</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.068</v>
+        <v>-2.4008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005</v>
+        <v>-0.0767</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0215</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3103</v>
+        <v>0.2752</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2062</v>
+        <v>0.461</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1041</v>
+        <v>-0.1858</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7312</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.0162</v>
+        <v>9.3187</v>
       </c>
       <c r="E12" t="n">
-        <v>14.2427</v>
+        <v>14.54529999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.2266</v>
+        <v>-5.226500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>7.325799999999999</v>
@@ -1378,10 +1378,10 @@
         <v>-11.7995</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.003899999999999876</v>
+        <v>-0.00389999999999982</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9766000000000004</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.6972</v>
@@ -1390,16 +1390,16 @@
         <v>13.6741</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0457</v>
+        <v>1.3482</v>
       </c>
       <c r="T12" t="n">
-        <v>2.546</v>
+        <v>2.8486</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5005</v>
+        <v>-1.5006</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3321999999999995</v>
+        <v>-0.3321999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>5.2644</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3874</v>
+        <v>4.8555</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9104</v>
+        <v>4.8092</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.523</v>
+        <v>0.0462</v>
       </c>
       <c r="G13" t="n">
         <v>0.6371</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6284</v>
+        <v>-0.1603</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3936</v>
+        <v>0.2925</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.022</v>
+        <v>-0.4528</v>
       </c>
       <c r="V13" t="n">
         <v>3.988</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5215</v>
+        <v>1.8073</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1112</v>
+        <v>2.9989</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5897</v>
+        <v>-1.1916</v>
       </c>
       <c r="G14" t="n">
         <v>1.6146</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2156</v>
+        <v>1.5015</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9234</v>
+        <v>0.8111</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2923</v>
+        <v>0.6904</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3321</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0235</v>
+        <v>0.4889</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7413999999999999</v>
+        <v>1.0448</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7179</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.5037</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5816</v>
+        <v>-0.1162</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1594</v>
+        <v>0.1439</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4222</v>
+        <v>-0.2601</v>
       </c>
       <c r="V15" t="n">
         <v>0.6642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9444</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0601</v>
+        <v>1.4282</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8843</v>
+        <v>-2.1706</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4881</v>
+        <v>-1.7004</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6633</v>
+        <v>0.4441</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1753</v>
+        <v>-2.1445</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0609</v>
+        <v>-0.2472</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0205</v>
+        <v>1.7613</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>-2.0085</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.549</v>
+        <v>-1.4532</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6838</v>
+        <v>-1.3172</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1348</v>
+        <v>-0.136</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2377</v>
+        <v>-0.7415</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.121</v>
+        <v>-0.1526</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1167</v>
+        <v>-0.589</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>0.3321</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3553</v>
+        <v>-0.7823</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4904</v>
+        <v>-0.0601</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8457</v>
+        <v>-0.7222</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4656</v>
+        <v>-0.4881</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0727</v>
+        <v>-0.6633</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5383</v>
+        <v>0.1753</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3961</v>
+        <v>0.0609</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3152</v>
+        <v>0.0205</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8617</v>
+        <v>-0.549</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2425</v>
+        <v>-0.6838</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6192</v>
+        <v>0.1348</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8331</v>
+        <v>-0.0757</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7705</v>
+        <v>-0.121</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0626</v>
+        <v>0.0454</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9414</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8366</v>
+        <v>-1.7805</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8215</v>
+        <v>0.9849</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6581</v>
+        <v>-2.7653</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7004</v>
+        <v>-0.4656</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4441</v>
+        <v>1.0727</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1445</v>
+        <v>-1.5383</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2472</v>
+        <v>2.3961</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7613</v>
+        <v>2.3152</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0085</v>
+        <v>0.0809</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4532</v>
+        <v>-2.8617</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3172</v>
+        <v>-1.2425</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.136</v>
+        <v>-1.6192</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8357</v>
+        <v>0.4079</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7592</v>
+        <v>0.2649</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0765</v>
+        <v>0.143</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2091</v>
+        <v>-2.4069</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7719</v>
+        <v>-0.8636</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4373</v>
+        <v>-1.5432</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0138</v>
+        <v>-1.9627</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7439</v>
+        <v>0.0061</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2698</v>
+        <v>-1.9688</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6741</v>
+        <v>1.3041</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6741</v>
+        <v>0.8442</v>
       </c>
       <c r="L19" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-3.2668</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.838</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.4287</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>-0.3397</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.0698</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.2698</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.586</v>
-      </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3907</v>
+        <v>-0.3893</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.121</v>
+        <v>0.0359</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2696</v>
+        <v>-0.4252</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>-0.0549</v>
       </c>
       <c r="W19" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3234</v>
+        <v>-3.2091</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6725</v>
+        <v>-1.7719</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6508</v>
+        <v>-1.4373</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9627</v>
+        <v>-1.0138</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0061</v>
+        <v>-0.7439</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9688</v>
+        <v>-0.2698</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3041</v>
+        <v>-0.6741</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8442</v>
+        <v>-0.6741</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2668</v>
+        <v>-0.3397</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.838</v>
+        <v>-0.0698</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.4287</v>
+        <v>-0.2698</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.2696</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.1488</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.1488</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-1.3058</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.773</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.5328000000000001</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-0.0549</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.0549</v>
-      </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2797</v>
+        <v>-5.8984</v>
       </c>
       <c r="E21" t="n">
         <v>-3.3439</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9358</v>
+        <v>-2.5545</v>
       </c>
       <c r="G21" t="n">
         <v>-5.4509</v>
@@ -2092,13 +2092,13 @@
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1144</v>
+        <v>0.2669</v>
       </c>
       <c r="T21" t="n">
         <v>0.3469</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4612</v>
+        <v>-0.0799</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.016099999999998</v>
+        <v>-7.667899999999999</v>
       </c>
       <c r="E22" t="n">
         <v>5.2265</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.2426</v>
+        <v>-12.8944</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.3261</v>
+        <v>-7.326099999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>3.467800000000001</v>
+        <v>3.4678</v>
       </c>
       <c r="I22" t="n">
         <v>-10.7934</v>
@@ -2149,7 +2149,7 @@
         <v>11.7996</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003899999999999714</v>
+        <v>0.003899999999999937</v>
       </c>
       <c r="M22" t="n">
         <v>-19.1294</v>
@@ -2170,16 +2170,16 @@
         <v>12.6973</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.045600000000001</v>
+        <v>0.3026000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5008</v>
+        <v>1.5006</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.5461</v>
+        <v>-1.1978</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3321000000000001</v>
+        <v>0.3320999999999998</v>
       </c>
       <c r="W22" t="n">
         <v>5.5964</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484266_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484266_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6231</v>
+        <v>4.2192</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8957</v>
+        <v>4.8062</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2726</v>
+        <v>-0.5869</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8819</v>
+        <v>2.4569</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0215</v>
+        <v>1.0136</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8604</v>
+        <v>1.4433</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5674</v>
+        <v>4.5091</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4367</v>
+        <v>1.9864</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1307</v>
+        <v>2.5227</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6854</v>
+        <v>-2.0522</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.4152</v>
+        <v>-0.9729</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2702</v>
+        <v>-1.0793</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2332</v>
+        <v>-0.194</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3599</v>
+        <v>0.0551</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1267</v>
+        <v>-0.2491</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0549</v>
+        <v>1.7609</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0549</v>
+        <v>1.2186</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.5423</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +653,72 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2192</v>
+        <v>3.4021</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8062</v>
+        <v>3.6747</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5869</v>
+        <v>-0.2726</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4569</v>
+        <v>1.661</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0136</v>
+        <v>-0.5925</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4433</v>
+        <v>2.2534</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5091</v>
+        <v>4.3464</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9864</v>
+        <v>1.8227</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5227</v>
+        <v>2.5237</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0522</v>
+        <v>-2.6854</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9729</v>
+        <v>-2.4152</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0793</v>
+        <v>-0.2702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.194</v>
+        <v>0.2332</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0551</v>
+        <v>0.3599</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2491</v>
+        <v>-0.1267</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7609</v>
+        <v>-0.0549</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>-0.0549</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5423</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.441</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-0.7312</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CARRERA PRAT</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0828</v>
+        <v>1.221</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.221</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8885</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8027</v>
+        <v>1.221</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0205</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7823</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6679</v>
+        <v>1.221</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6475</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3033</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3033</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>J. CARRERA PRAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9464</v>
+        <v>0.0828</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0092</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9372</v>
+        <v>-0.8885</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8032</v>
+        <v>0.8027</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6388</v>
+        <v>0.0205</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8356</v>
+        <v>0.7823</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9186</v>
+        <v>0.6679</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9171</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8358</v>
+        <v>0.6475</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7219</v>
+        <v>0.1348</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7217</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0002</v>
+        <v>0.1348</v>
       </c>
       <c r="P9" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2166</v>
+        <v>0.3033</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0489</v>
+        <v>0.3033</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2656</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4009</v>
+        <v>-0.9464</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6015</v>
+        <v>-0.0092</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2006</v>
+        <v>-0.9372</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1245</v>
+        <v>-0.8032</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2305</v>
+        <v>-2.6388</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.106</v>
+        <v>1.8356</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9031</v>
+        <v>0.9186</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0085</v>
+        <v>-0.9171</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1054</v>
+        <v>1.8358</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7785</v>
+        <v>-1.7219</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7779</v>
+        <v>-1.7217</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2689</v>
+        <v>-0.2166</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4534</v>
+        <v>0.0489</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1845</v>
+        <v>-0.2656</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4502</v>
+        <v>-0.1219</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0511</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3991</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4775</v>
+        <v>-2.4009</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4008</v>
+        <v>-2.6015</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0767</v>
+        <v>0.2006</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0215</v>
+        <v>1.1245</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7529</v>
+        <v>2.2305</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2687</v>
+        <v>-1.106</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9084</v>
+        <v>1.9031</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7752</v>
+        <v>3.0085</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1332</v>
+        <v>-1.1054</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1131</v>
+        <v>-0.7785</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9777</v>
+        <v>-0.7779</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1354</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2752</v>
+        <v>0.2689</v>
       </c>
       <c r="T11" t="n">
-        <v>0.461</v>
+        <v>0.4534</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1858</v>
+        <v>-0.1845</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7312</v>
+        <v>-1.4502</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.0511</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7312</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.3187</v>
+        <v>-2.4775</v>
       </c>
       <c r="E12" t="n">
-        <v>14.54529999999999</v>
+        <v>-2.4008</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.226500000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="G12" t="n">
-        <v>7.325799999999999</v>
+        <v>-2.0215</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.467499999999999</v>
+        <v>-1.7529</v>
       </c>
       <c r="I12" t="n">
-        <v>10.7934</v>
+        <v>-0.2687</v>
       </c>
       <c r="J12" t="n">
-        <v>19.1293</v>
+        <v>-0.9084</v>
       </c>
       <c r="K12" t="n">
-        <v>8.332000000000001</v>
+        <v>-0.7752</v>
       </c>
       <c r="L12" t="n">
-        <v>10.7976</v>
+        <v>-0.1332</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.8034</v>
+        <v>-1.1131</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.7995</v>
+        <v>-0.9777</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.00389999999999982</v>
+        <v>-0.1354</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9765999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6972</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>13.6741</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3482</v>
+        <v>0.2752</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8486</v>
+        <v>0.461</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5006</v>
+        <v>-0.1858</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3321999999999999</v>
+        <v>-0.7312</v>
       </c>
       <c r="W12" t="n">
-        <v>5.2644</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.5965</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8555</v>
+        <v>9.3187</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8092</v>
+        <v>14.5453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0462</v>
+        <v>-5.2265</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6371</v>
+        <v>7.325899999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2924</v>
+        <v>-3.467499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9295</v>
+        <v>10.7934</v>
       </c>
       <c r="J13" t="n">
-        <v>2.365</v>
+        <v>19.1293</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0296</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3354</v>
+        <v>10.7976</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7279</v>
+        <v>-11.8034</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3221</v>
+        <v>-11.7995</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4058</v>
+        <v>-0.003899999999999793</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3907</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1721</v>
+        <v>-12.6972</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>13.6741</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1603</v>
+        <v>1.3482</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2925</v>
+        <v>2.8486</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4528</v>
+        <v>-1.5006</v>
       </c>
       <c r="V13" t="n">
-        <v>3.988</v>
+        <v>-0.3321999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3238</v>
+        <v>5.2644</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
-      </c>
+        <v>-5.596500000000001</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8073</v>
+        <v>4.8555</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9989</v>
+        <v>4.8092</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1916</v>
+        <v>0.0462</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6146</v>
+        <v>0.6371</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0049</v>
+        <v>-0.2924</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3902</v>
+        <v>0.9295</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0909</v>
+        <v>2.365</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3221</v>
+        <v>1.0296</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7688</v>
+        <v>1.3354</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.4763</v>
+        <v>-1.7279</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3172</v>
+        <v>-1.3221</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1591</v>
+        <v>-0.4058</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5015</v>
+        <v>-0.1603</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8111</v>
+        <v>0.2925</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6904</v>
+        <v>-0.4528</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3321</v>
+        <v>3.988</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2224</v>
+        <v>3.3238</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4889</v>
+        <v>1.8073</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0448</v>
+        <v>2.9989</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.1916</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5037</v>
+        <v>1.6146</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0533</v>
+        <v>3.0049</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5495</v>
+        <v>-1.3902</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0264</v>
+        <v>5.0909</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6867</v>
+        <v>4.3221</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6603</v>
+        <v>0.7688</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5226</v>
+        <v>-3.4763</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6334</v>
+        <v>-1.3172</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8893</v>
+        <v>-2.1591</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q15" t="n">
         <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1162</v>
+        <v>1.5015</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1439</v>
+        <v>0.8111</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2601</v>
+        <v>0.6904</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>-0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7423999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4282</v>
+        <v>0.921</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1706</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7004</v>
+        <v>0.921</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4441</v>
+        <v>0.921</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1445</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2472</v>
+        <v>0.921</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7613</v>
+        <v>0.921</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.0085</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4532</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3172</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.136</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7415</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1526</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.589</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7823</v>
+        <v>0.4889</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0601</v>
+        <v>1.0448</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7222</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4881</v>
+        <v>1.5037</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6633</v>
+        <v>4.0533</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1753</v>
+        <v>-2.5495</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0609</v>
+        <v>4.0264</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0205</v>
+        <v>4.6867</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-0.6603</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.549</v>
+        <v>-2.5226</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6838</v>
+        <v>-0.6334</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>-1.8893</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0757</v>
+        <v>-0.1162</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>0.1439</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0454</v>
+        <v>-0.2601</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7805</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9849</v>
+        <v>1.4282</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7653</v>
+        <v>-2.1706</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4656</v>
+        <v>-1.7004</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0727</v>
+        <v>0.4441</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5383</v>
+        <v>-2.1445</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3961</v>
+        <v>-0.2472</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3152</v>
+        <v>1.7613</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-2.0085</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8617</v>
+        <v>-1.4532</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2425</v>
+        <v>-1.3172</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6192</v>
+        <v>-0.136</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4079</v>
+        <v>-0.7415</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2649</v>
+        <v>-0.1526</v>
       </c>
       <c r="U18" t="n">
-        <v>0.143</v>
+        <v>-0.589</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>1.8279</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4069</v>
+        <v>-0.7823</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8636</v>
+        <v>-0.0601</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5432</v>
+        <v>-0.7222</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9627</v>
+        <v>-0.4881</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0061</v>
+        <v>-0.6633</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9688</v>
+        <v>0.1753</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3041</v>
+        <v>0.0609</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8442</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4599</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2668</v>
+        <v>-0.549</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.838</v>
+        <v>-0.6838</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4287</v>
+        <v>0.1348</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3893</v>
+        <v>-0.0757</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0359</v>
+        <v>-0.121</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4252</v>
+        <v>0.0454</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0549</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2091</v>
+        <v>-1.7805</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7719</v>
+        <v>0.9849</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4373</v>
+        <v>-2.7653</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0138</v>
+        <v>-0.4656</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7439</v>
+        <v>1.0727</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2698</v>
+        <v>-1.5383</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6741</v>
+        <v>2.3961</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6741</v>
+        <v>2.3152</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3397</v>
+        <v>-2.8617</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0698</v>
+        <v>-1.2425</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2698</v>
+        <v>-1.6192</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3907</v>
+        <v>0.4079</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.121</v>
+        <v>0.2649</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2696</v>
+        <v>0.143</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8984</v>
+        <v>-2.4069</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3439</v>
+        <v>-0.8636</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5545</v>
+        <v>-1.5432</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.4509</v>
+        <v>-1.9627</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.4137</v>
+        <v>0.0061</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0371</v>
+        <v>-1.9688</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5187</v>
+        <v>1.3041</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.5059</v>
+        <v>0.8442</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0128</v>
+        <v>0.4599</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9322</v>
+        <v>-3.2668</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9079</v>
+        <v>-0.838</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0243</v>
+        <v>-2.4287</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2669</v>
+        <v>-0.3893</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3469</v>
+        <v>0.0359</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0799</v>
+        <v>-0.4252</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>-0.0549</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,235 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.667899999999999</v>
+        <v>-3.2091</v>
       </c>
       <c r="E22" t="n">
-        <v>5.2265</v>
+        <v>-1.7719</v>
       </c>
       <c r="F22" t="n">
+        <v>-1.4373</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.0138</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.7439</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.3397</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.2696</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P. MONES RIERA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-6.8194</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-4.2648</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.5545</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-6.3718</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-4.3347</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.0371</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-3.4396</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-3.4268</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.9322</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.9079</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-2.0243</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.0799</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484266_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-7.667900000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.226599999999999</v>
+      </c>
+      <c r="F24" t="n">
         <v>-12.8944</v>
       </c>
-      <c r="G22" t="n">
-        <v>-7.326099999999999</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="G24" t="n">
+        <v>-7.326</v>
+      </c>
+      <c r="H24" t="n">
         <v>3.4678</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I24" t="n">
         <v>-10.7934</v>
       </c>
-      <c r="J22" t="n">
-        <v>11.8034</v>
-      </c>
-      <c r="K22" t="n">
-        <v>11.7996</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J24" t="n">
+        <v>11.8035</v>
+      </c>
+      <c r="K24" t="n">
+        <v>11.7997</v>
+      </c>
+      <c r="L24" t="n">
         <v>0.003899999999999937</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>-19.1294</v>
       </c>
-      <c r="N22" t="n">
-        <v>-8.331899999999999</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="N24" t="n">
+        <v>-8.331900000000001</v>
+      </c>
+      <c r="O24" t="n">
         <v>-10.7974</v>
       </c>
-      <c r="P22" t="n">
-        <v>-0.9766</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P24" t="n">
+        <v>-0.9765999999999996</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-13.6741</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>0.3026000000000001</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>1.5006</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>-1.1978</v>
       </c>
-      <c r="V22" t="n">
-        <v>0.3320999999999998</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="V24" t="n">
+        <v>0.3321000000000003</v>
+      </c>
+      <c r="W24" t="n">
         <v>5.5964</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X24" t="n">
         <v>-5.2644</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
